--- a/branches/fix/publish-simplifier-rebased/ValueSet-mii-vs-molgen-familiaere-linie.xlsx
+++ b/branches/fix/publish-simplifier-rebased/ValueSet-mii-vs-molgen-familiaere-linie.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T15:40:47+00:00</t>
+    <t>2026-09-07T15:58:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
